--- a/data/trans_orig/IP12_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Estudios-trans_orig.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables originales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,12 +524,18 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si en las últimas 2 semanas limitaron su actividad por dolores o síntomas en 2023 (Tasa respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas limitaron su actividad por dolores o síntomas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -542,24 +548,30 @@
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="M1" s="3" t="n"/>
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,65 +588,95 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -658,6 +700,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -667,70 +715,112 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>3560</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2725</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>6831</v>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6831</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3531</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12495</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>11,02%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>5,69%</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>10391</v>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>9556</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>4866</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>15539</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -738,70 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>51118</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>55173</v>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>106291</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>2768</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -809,216 +941,342 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>54678</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51118</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>53470</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>62004</v>
+          <t>93,49%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>86,74%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>55173</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>116682</v>
+          <t>49509</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>58473</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>88,98%</t>
+        </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>106291</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>99848</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>110921</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>85,57%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>32015</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>54678</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>38702</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>62004</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>70717</v>
+          <t>62004</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>62004</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>116682</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>116682</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>116682</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>590</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>427679</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21927</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>601</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>477917</v>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>27061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>1191</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>905596</v>
+          <t>18779</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39140</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>48988</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>37531</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>63090</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -1026,145 +1284,225 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>642</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>459694</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>10088</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>15660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>656</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>516619</v>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>1298</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>976313</v>
+          <t>6989</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>19593</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>21729</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>14511</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>31034</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>11697</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>427679</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>418082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>436623</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>13570</v>
+          <t>93,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>90,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,98%</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>601</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>477917</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>25268</v>
+          <t>465550</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>488097</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>92,51%</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>905596</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>891115</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>919570</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>92,76%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -1172,216 +1510,342 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>211</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>137854</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>459694</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>459694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>459694</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>222</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>169779</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>656</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>516619</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>433</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>307632</v>
+          <t>516619</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>516619</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>976313</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>976313</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>976313</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n"/>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>230</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>149551</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7898</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>238</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>183349</v>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,4%</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11643</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>468</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>332900</v>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>19720</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>19542</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>13001</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>28979</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>47272</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3799</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>59103</v>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>106375</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6135</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>5726</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>11744</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1392,67 +1856,109 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>864</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>616651</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>137854</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>131847</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>142212</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>897</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>702869</v>
+          <t>92,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>222</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>169779</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>1761</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>1319520</v>
+          <t>161209</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>175044</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>92,6%</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>307632</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>297439</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>315289</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>92,41%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>89,35%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -1463,20 +1969,24 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>941</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>663923</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>149551</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1484,32 +1994,40 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>977</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>761972</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>238</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>183349</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>1918</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>1425895</v>
+          <t>183349</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>183349</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1522,13 +2040,499 @@
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>332900</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>332900</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>332900</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>32551</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23837</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42996</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>45535</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>33747</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>78086</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>63871</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>95229</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14721</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9260</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22226</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>13568</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>8264</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>21555</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>28290</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>20149</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>38833</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>616651</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>604302</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>627463</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>92,88%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>91,02%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>94,51%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>702869</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>687116</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>714365</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>90,18%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>93,75%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>1761</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>1319520</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>1298976</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>1336497</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>92,54%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>91,1%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>93,73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>663923</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>663923</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>663923</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1918</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1425895</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>1425895</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>1425895</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1536,14 +2540,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IP12_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12495</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>46518</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53470</t>
+          <t>53243</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>49333</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58473</t>
+          <t>58410</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>99848</t>
+          <t>100208</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>110921</t>
+          <t>110666</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>14948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30945</t>
+          <t>30034</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18779</t>
+          <t>18834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39140</t>
+          <t>37529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37531</t>
+          <t>37598</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63090</t>
+          <t>62848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19593</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31034</t>
+          <t>31841</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>418082</t>
+          <t>418321</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>436623</t>
+          <t>437407</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>465550</t>
+          <t>465644</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>488097</t>
+          <t>488056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>891115</t>
+          <t>889432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>919570</t>
+          <t>919371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12566</t>
+          <t>13051</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13001</t>
+          <t>13084</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28979</t>
+          <t>28237</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>131847</t>
+          <t>131128</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142212</t>
+          <t>141949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161209</t>
+          <t>161726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175044</t>
+          <t>175454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>297439</t>
+          <t>298658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315289</t>
+          <t>314920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23837</t>
+          <t>24916</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42996</t>
+          <t>43140</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33747</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58792</t>
+          <t>59646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63871</t>
+          <t>64839</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95229</t>
+          <t>94421</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>21945</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20149</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38833</t>
+          <t>39177</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>604302</t>
+          <t>604837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>627463</t>
+          <t>626821</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>687116</t>
+          <t>689239</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>714365</t>
+          <t>716087</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1298976</t>
+          <t>1301201</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1336497</t>
+          <t>1336576</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP12_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12392</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,68%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6615</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2592</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6393</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>13,67%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>9217</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>5158</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>15375</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>4,98%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6831</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3594</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12671</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>20,44%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>9556</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>15547</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3292</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3059</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -946,74 +946,74 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50107</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>44340</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53333</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>88,32%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>78,16%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>94,01%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>51118</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46518</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53243</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>85,08%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>43441</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>39350</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>84,16%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>97,37%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>55173</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>49333</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>58410</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>88,98%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>79,56%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>137</t>
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>106291</t>
+          <t>93548</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>100208</t>
+          <t>87041</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>110666</t>
+          <t>97557</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25021</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17120</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35955</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>21927</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14948</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30034</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>27061</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18834</t>
+          <t>15197</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37529</t>
+          <t>29639</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>48988</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37598</t>
+          <t>36239</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62848</t>
+          <t>59665</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>11281</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6429</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>18635</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>10088</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5813</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>15943</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>21729</t>
+          <t>21338</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>14755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>30580</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>439376</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>426061</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>448396</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>92,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>89,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>590</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>427679</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>418321</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>437407</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>91,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>477917</t>
+          <t>400221</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>465644</t>
+          <t>390689</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>488056</t>
+          <t>407957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>905596</t>
+          <t>839597</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>889432</t>
+          <t>826082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>919371</t>
+          <t>852221</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13051</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19320</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>18705</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>12383</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28237</t>
+          <t>26979</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1846</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5640</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3799</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1380</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8557</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>12252</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>155942</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>148091</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>161431</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>137854</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>131128</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>141949</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,18%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>169779</t>
+          <t>138026</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161726</t>
+          <t>131513</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175454</t>
+          <t>142655</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>307632</t>
+          <t>293968</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>298658</t>
+          <t>284043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>314920</t>
+          <t>301003</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42278</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31638</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>56786</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>32551</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>24916</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>43140</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>45535</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34598</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59646</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>78086</t>
+          <t>74268</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64839</t>
+          <t>60910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94421</t>
+          <t>91909</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7972</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>20665</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>14721</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>9405</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>21945</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>14659</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>22309</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>19686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39177</t>
+          <t>37443</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>645425</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>630717</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>657163</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>92,09%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>90,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>864</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>616651</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>604837</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>626821</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>91,1%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>94,41%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>702869</t>
+          <t>581687</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>689239</t>
+          <t>570373</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>716087</t>
+          <t>592718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1319520</t>
+          <t>1227112</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1301201</t>
+          <t>1208030</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1336576</t>
+          <t>1243611</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
